--- a/matrices/MATRICE_DE_SUIVI_DES_ACTIVITES_du_28-09-26.xlsx
+++ b/matrices/MATRICE_DE_SUIVI_DES_ACTIVITES_du_28-09-26.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\osow\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\H4KB1JL3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HpEliteBook\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B49F65-CB9F-4D49-A053-6A9A67479A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9BC59F-DE83-4227-832E-4717CA5C53F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MATRICE DE SUIVI" sheetId="1" r:id="rId1"/>
+    <sheet name="Base suivi" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="303">
   <si>
     <t>MATRICE DE SUIVI DES ACTIVITES</t>
   </si>
@@ -668,12 +669,441 @@
   <si>
     <t>Taux d'exécution</t>
   </si>
+  <si>
+    <t xml:space="preserve">Photo  preuve </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nom prenoms + poste et structure </t>
+  </si>
+  <si>
+    <t>MONTANT DECAISSE</t>
+  </si>
+  <si>
+    <t>TAUX D'EXECUTION FINANCIERE</t>
+  </si>
+  <si>
+    <t>VOLUME ACHEVE</t>
+  </si>
+  <si>
+    <t>UTILISATION DU BUDGET</t>
+  </si>
+  <si>
+    <t>JAUGE D'ACHEVEMENT</t>
+  </si>
+  <si>
+    <t>MOAMBISSO</t>
+  </si>
+  <si>
+    <t>ZOUMASSADOUGOU</t>
+  </si>
+  <si>
+    <t>OUROSSANISSO</t>
+  </si>
+  <si>
+    <t>SINGOSSO</t>
+  </si>
+  <si>
+    <t>GUENIMANZO</t>
+  </si>
+  <si>
+    <t>FENAN 2</t>
+  </si>
+  <si>
+    <t>GANHOUE</t>
+  </si>
+  <si>
+    <t>OUALOU</t>
+  </si>
+  <si>
+    <t>SABOUDOUGOU</t>
+  </si>
+  <si>
+    <t>TIAHOUE</t>
+  </si>
+  <si>
+    <t>BAYA</t>
+  </si>
+  <si>
+    <t>PONONDOUGOU</t>
+  </si>
+  <si>
+    <t>LANDIOUGOU</t>
+  </si>
+  <si>
+    <t>SANAHOULE</t>
+  </si>
+  <si>
+    <t>SIANHALA</t>
+  </si>
+  <si>
+    <t>TABAKORONI</t>
+  </si>
+  <si>
+    <t>KANTARA</t>
+  </si>
+  <si>
+    <t>LEASSO</t>
+  </si>
+  <si>
+    <t>GBEMA</t>
+  </si>
+  <si>
+    <t>MISSIDOUGOU</t>
+  </si>
+  <si>
+    <t>KOUASSIDOUGOU</t>
+  </si>
+  <si>
+    <t>GBOROZOMBA</t>
+  </si>
+  <si>
+    <t>LIGBISSO</t>
+  </si>
+  <si>
+    <t>DANDOUGOU</t>
+  </si>
+  <si>
+    <t>DIHINTEDOU</t>
+  </si>
+  <si>
+    <t>SYALEDOUO</t>
+  </si>
+  <si>
+    <t>YOUTOURDOUO</t>
+  </si>
+  <si>
+    <t>PIAYE</t>
+  </si>
+  <si>
+    <t>LANKIO</t>
+  </si>
+  <si>
+    <t>TOTOBIKERNO</t>
+  </si>
+  <si>
+    <t>LAGBO-TADJOTE</t>
+  </si>
+  <si>
+    <t>NIAMOIN</t>
+  </si>
+  <si>
+    <t>BOUDOU</t>
+  </si>
+  <si>
+    <t>KIRAMISSE</t>
+  </si>
+  <si>
+    <t>GANSE</t>
+  </si>
+  <si>
+    <t>WASSIDE</t>
+  </si>
+  <si>
+    <t>NAGUINA</t>
+  </si>
+  <si>
+    <t>GOUEYA</t>
+  </si>
+  <si>
+    <t>TOKALA</t>
+  </si>
+  <si>
+    <t>OUELLI</t>
+  </si>
+  <si>
+    <t>AMODI</t>
+  </si>
+  <si>
+    <t>YAOKOKOROKO</t>
+  </si>
+  <si>
+    <t>WAKIALA</t>
+  </si>
+  <si>
+    <t>NAGAFOU</t>
+  </si>
+  <si>
+    <t>DIASSAMPA</t>
+  </si>
+  <si>
+    <t>KOMOEKRO</t>
+  </si>
+  <si>
+    <t>KOUADJAKRO</t>
+  </si>
+  <si>
+    <t>YOBOUAKRO</t>
+  </si>
+  <si>
+    <t>DOKANOU</t>
+  </si>
+  <si>
+    <t>LOUGBONOU 2</t>
+  </si>
+  <si>
+    <t>TOURO</t>
+  </si>
+  <si>
+    <t>YODANKAHA</t>
+  </si>
+  <si>
+    <t>ATTIENKAHA</t>
+  </si>
+  <si>
+    <t>NIEDIEKAHA</t>
+  </si>
+  <si>
+    <t>SEPIKAHA</t>
+  </si>
+  <si>
+    <t>SELILEKAHA</t>
+  </si>
+  <si>
+    <t>NAHOLO</t>
+  </si>
+  <si>
+    <t>LAHOGORA</t>
+  </si>
+  <si>
+    <t>FENGOLO</t>
+  </si>
+  <si>
+    <t>KAKORO</t>
+  </si>
+  <si>
+    <t>TIEBALA</t>
+  </si>
+  <si>
+    <t>KADIASSO</t>
+  </si>
+  <si>
+    <t>TIEKORODOUGOU</t>
+  </si>
+  <si>
+    <t>SOKORODOUGOU</t>
+  </si>
+  <si>
+    <t>SARALA</t>
+  </si>
+  <si>
+    <t>MASSADOUGOU</t>
+  </si>
+  <si>
+    <t>KARAFINE</t>
+  </si>
+  <si>
+    <t>NOGOTAHA</t>
+  </si>
+  <si>
+    <t>TAPRE</t>
+  </si>
+  <si>
+    <t>KADIOHA</t>
+  </si>
+  <si>
+    <t>FARAKORO</t>
+  </si>
+  <si>
+    <t>PIGNON</t>
+  </si>
+  <si>
+    <t>LITIO</t>
+  </si>
+  <si>
+    <t>KARAFIGUE</t>
+  </si>
+  <si>
+    <t>KOKAHA</t>
+  </si>
+  <si>
+    <t>DAGBAPLE</t>
+  </si>
+  <si>
+    <t>TAHOUARA</t>
+  </si>
+  <si>
+    <t>SOHOUO</t>
+  </si>
+  <si>
+    <t>M'BALLA</t>
+  </si>
+  <si>
+    <t>KOROWITA</t>
+  </si>
+  <si>
+    <t>SOKOLO</t>
+  </si>
+  <si>
+    <t>KAWERE</t>
+  </si>
+  <si>
+    <t>KONIERE</t>
+  </si>
+  <si>
+    <t>BOUGOU</t>
+  </si>
+  <si>
+    <t>NAFOUNGOLO</t>
+  </si>
+  <si>
+    <t>GBINZO</t>
+  </si>
+  <si>
+    <t>DJELISSO</t>
+  </si>
+  <si>
+    <t>SEPENEDJOKAHA</t>
+  </si>
+  <si>
+    <t>DIOMANDOUGOU</t>
+  </si>
+  <si>
+    <t>MADJI</t>
+  </si>
+  <si>
+    <t>LIPARA</t>
+  </si>
+  <si>
+    <t>KATOGBO</t>
+  </si>
+  <si>
+    <t>GBOHOVO</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>BANANDJE</t>
+  </si>
+  <si>
+    <t>DIARABANA</t>
+  </si>
+  <si>
+    <t>MONGBARA</t>
+  </si>
+  <si>
+    <t>MARHANA</t>
+  </si>
+  <si>
+    <t>KAVALA</t>
+  </si>
+  <si>
+    <t>SELECT IVOIRE MULTISERVICES SARL</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>NOUVEAU SERVICES INTERNATIONAL COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Non démarré</t>
+  </si>
+  <si>
+    <t>Pas de PGES</t>
+  </si>
+  <si>
+    <t>Aucune ONG</t>
+  </si>
+  <si>
+    <t>KONINGOUELO</t>
+  </si>
+  <si>
+    <t>MASSALA-BARALA</t>
+  </si>
+  <si>
+    <t>Démarrage autorisé</t>
+  </si>
+  <si>
+    <t>NOUKPARADOUGOU</t>
+  </si>
+  <si>
+    <t>MAHALE</t>
+  </si>
+  <si>
+    <t>DEMBASSO</t>
+  </si>
+  <si>
+    <t>BOAYAOKRO-BLIPLA</t>
+  </si>
+  <si>
+    <t>DIALAKORO</t>
+  </si>
+  <si>
+    <t>DANGBASSO</t>
+  </si>
+  <si>
+    <t>LINGUEKORO</t>
+  </si>
+  <si>
+    <t>KIMBIRILA NORD</t>
+  </si>
+  <si>
+    <t>Erreur et Reprise de l'OS</t>
+  </si>
+  <si>
+    <t>MADIANA SOKORANI</t>
+  </si>
+  <si>
+    <t>N'DRAMAKRO</t>
+  </si>
+  <si>
+    <t>NAGBO-DONGO</t>
+  </si>
+  <si>
+    <t>LOUGBONOU 1</t>
+  </si>
+  <si>
+    <t>KPANA KALO</t>
+  </si>
+  <si>
+    <t>Mobilisée</t>
+  </si>
+  <si>
+    <t>SOKALA SOBARA</t>
+  </si>
+  <si>
+    <t>Non encore démarré</t>
+  </si>
+  <si>
+    <t>SARAKORODOUGOU</t>
+  </si>
+  <si>
+    <t>TOUGOUSSO</t>
+  </si>
+  <si>
+    <t>Centre de santé PIETRO BONILI</t>
+  </si>
+  <si>
+    <t>TINDIKORO-SOKOURA</t>
+  </si>
+  <si>
+    <t>Solidarité</t>
+  </si>
+  <si>
+    <t>Démarrage non effectif</t>
+  </si>
+  <si>
+    <t>KENEGBE SUD</t>
+  </si>
+  <si>
+    <t>KENEGBE NORD</t>
+  </si>
+  <si>
+    <t>GBALO-KANDJI</t>
+  </si>
+  <si>
+    <t>DJENIGBE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -756,8 +1186,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -791,6 +1228,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -856,11 +1299,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1000,16 +1444,25 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1026,18 +1479,23 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{063E3A05-25B4-49FF-9441-0B8563A481F3}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1311,51 +1769,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AF161"/>
+  <dimension ref="B1:AJ161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14.33203125" style="6" customWidth="1"/>
     <col min="3" max="3" width="20.88671875" style="7" customWidth="1"/>
     <col min="4" max="4" width="20.21875" style="6" customWidth="1"/>
     <col min="5" max="5" width="42.21875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="21.77734375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" style="8" customWidth="1"/>
-    <col min="10" max="11" width="27.109375" style="8" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" style="10" customWidth="1"/>
-    <col min="13" max="13" width="26.77734375" style="6" customWidth="1"/>
-    <col min="14" max="15" width="22.6640625" style="9" customWidth="1"/>
-    <col min="16" max="16" width="14.77734375" customWidth="1"/>
-    <col min="17" max="17" width="13.88671875" customWidth="1"/>
-    <col min="18" max="32" width="11" style="11"/>
+    <col min="6" max="8" width="21.44140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" style="8" customWidth="1"/>
+    <col min="12" max="14" width="27.109375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="10" customWidth="1"/>
+    <col min="16" max="16" width="26.77734375" style="6" customWidth="1"/>
+    <col min="17" max="18" width="22.6640625" style="9" customWidth="1"/>
+    <col min="19" max="19" width="14.77734375" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" customWidth="1"/>
+    <col min="21" max="21" width="22.6640625" customWidth="1"/>
+    <col min="22" max="22" width="21.44140625" style="11" customWidth="1"/>
+    <col min="23" max="36" width="11" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32">
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-    </row>
-    <row r="2" spans="2:32" ht="61.2">
+    <row r="1" spans="2:36">
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+    </row>
+    <row r="2" spans="2:36" ht="61.2">
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
       <c r="D2" s="13"/>
       <c r="E2" s="12"/>
       <c r="F2" s="15"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18" t="s">
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-    </row>
-    <row r="3" spans="2:32" s="1" customFormat="1" ht="62.4">
+      <c r="L2" s="16"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+    </row>
+    <row r="3" spans="2:36" s="1" customFormat="1" ht="62.4">
       <c r="B3" s="19"/>
       <c r="C3" s="19" t="s">
         <v>1</v>
@@ -1370,43 +1835,53 @@
         <v>4</v>
       </c>
       <c r="G3" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="J3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="K3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="L3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="M3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="N3" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="O3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="P3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="Q3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="R3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="S3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="T3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
+      <c r="U3" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="V3" s="19" t="s">
+        <v>161</v>
+      </c>
       <c r="W3" s="21"/>
       <c r="X3" s="21"/>
       <c r="Y3" s="21"/>
@@ -1417,12 +1892,16 @@
       <c r="AD3" s="21"/>
       <c r="AE3" s="21"/>
       <c r="AF3" s="21"/>
-    </row>
-    <row r="4" spans="2:32" s="2" customFormat="1" ht="90.6">
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="21"/>
+    </row>
+    <row r="4" spans="2:36" s="2" customFormat="1" ht="90.6">
       <c r="B4" s="22">
         <v>1</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="59" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="23" t="s">
@@ -1434,38 +1913,38 @@
       <c r="F4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="25" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="23" t="s">
+      <c r="K4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="23"/>
-      <c r="L4" s="26">
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="26">
         <v>0</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="P4" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="22" t="s">
+      <c r="Q4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="22" t="s">
+      <c r="R4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
@@ -1476,12 +1955,16 @@
       <c r="AD4" s="11"/>
       <c r="AE4" s="11"/>
       <c r="AF4" s="11"/>
-    </row>
-    <row r="5" spans="2:32" s="2" customFormat="1" ht="105">
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+    </row>
+    <row r="5" spans="2:36" s="2" customFormat="1" ht="105">
       <c r="B5" s="22">
         <v>2</v>
       </c>
-      <c r="C5" s="55"/>
+      <c r="C5" s="60"/>
       <c r="D5" s="23" t="s">
         <v>27</v>
       </c>
@@ -1491,41 +1974,46 @@
       <c r="F5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="29" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="23" t="s">
+      <c r="K5" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="M5" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="26">
+      <c r="N5" s="23"/>
+      <c r="O5" s="26">
         <v>0</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="P5" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="Q5" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="R5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-    </row>
-    <row r="6" spans="2:32" s="2" customFormat="1" ht="75">
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+    </row>
+    <row r="6" spans="2:36" s="2" customFormat="1" ht="75">
       <c r="B6" s="22">
         <v>3</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="54" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="23" t="s">
@@ -1537,39 +2025,44 @@
       <c r="F6" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="29" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="23" t="s">
+      <c r="K6" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="30">
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="30">
         <v>0.05</v>
       </c>
-      <c r="M6" s="27" t="s">
+      <c r="P6" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="22" t="s">
+      <c r="Q6" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="22" t="s">
+      <c r="R6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-    </row>
-    <row r="7" spans="2:32" s="2" customFormat="1" ht="105">
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+    </row>
+    <row r="7" spans="2:36" s="2" customFormat="1" ht="105">
       <c r="B7" s="22">
         <v>4</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="56"/>
       <c r="D7" s="23" t="s">
         <v>44</v>
       </c>
@@ -1579,37 +2072,42 @@
       <c r="F7" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="29" t="s">
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="31">
+      <c r="K7" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="31">
         <v>0</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="P7" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="Q7" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="O7" s="22" t="s">
+      <c r="R7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-    </row>
-    <row r="8" spans="2:32" s="3" customFormat="1" ht="60">
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+    </row>
+    <row r="8" spans="2:36" s="3" customFormat="1" ht="60">
       <c r="B8" s="32">
         <v>5</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="61" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="33" t="s">
@@ -1621,36 +2119,36 @@
       <c r="F8" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="34" t="s">
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="33" t="s">
+      <c r="K8" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="33"/>
-      <c r="L8" s="31">
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="31">
         <v>0</v>
       </c>
-      <c r="M8" s="33"/>
-      <c r="N8" s="22" t="s">
+      <c r="P8" s="33"/>
+      <c r="Q8" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="O8" s="22" t="s">
+      <c r="R8" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
@@ -1661,12 +2159,16 @@
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
-    </row>
-    <row r="9" spans="2:32" s="3" customFormat="1" ht="75">
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="2"/>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
+    </row>
+    <row r="9" spans="2:36" s="3" customFormat="1" ht="75">
       <c r="B9" s="32">
         <v>6</v>
       </c>
-      <c r="C9" s="59"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="33" t="s">
         <v>57</v>
       </c>
@@ -1676,36 +2178,36 @@
       <c r="F9" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="35" t="s">
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="33" t="s">
+      <c r="K9" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="33"/>
-      <c r="L9" s="26">
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="26">
         <v>0</v>
       </c>
-      <c r="M9" s="33"/>
-      <c r="N9" s="22" t="s">
+      <c r="P9" s="33"/>
+      <c r="Q9" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="22" t="s">
+      <c r="R9" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="33"/>
+      <c r="V9" s="33"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
@@ -1716,12 +2218,16 @@
       <c r="AD9" s="2"/>
       <c r="AE9" s="2"/>
       <c r="AF9" s="2"/>
-    </row>
-    <row r="10" spans="2:32" s="3" customFormat="1" ht="75">
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+    </row>
+    <row r="10" spans="2:36" s="3" customFormat="1" ht="75">
       <c r="B10" s="32">
         <v>7</v>
       </c>
-      <c r="C10" s="60"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="33" t="s">
         <v>57</v>
       </c>
@@ -1731,36 +2237,36 @@
       <c r="F10" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="35" t="s">
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="33" t="s">
+      <c r="K10" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="26">
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="26">
         <v>0</v>
       </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="22" t="s">
+      <c r="P10" s="36"/>
+      <c r="Q10" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="O10" s="22" t="s">
+      <c r="R10" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
@@ -1771,12 +2277,16 @@
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
       <c r="AF10" s="2"/>
-    </row>
-    <row r="11" spans="2:32" s="2" customFormat="1" ht="120">
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="2:36" s="2" customFormat="1" ht="120">
       <c r="B11" s="22">
         <v>8</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="54" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="23" t="s">
@@ -1788,39 +2298,44 @@
       <c r="F11" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="29" t="s">
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="23" t="s">
+      <c r="K11" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="30">
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="30">
         <v>0.05</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="P11" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="N11" s="22" t="s">
+      <c r="Q11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="O11" s="22" t="s">
+      <c r="R11" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-    </row>
-    <row r="12" spans="2:32" s="2" customFormat="1" ht="60">
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+    </row>
+    <row r="12" spans="2:36" s="2" customFormat="1" ht="60">
       <c r="B12" s="22">
         <v>9</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="23" t="s">
         <v>72</v>
       </c>
@@ -1830,37 +2345,42 @@
       <c r="F12" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="29" t="s">
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="I12" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="26">
+      <c r="K12" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="26">
         <v>0</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="P12" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="N12" s="22" t="s">
+      <c r="Q12" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="O12" s="22" t="s">
+      <c r="R12" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-    </row>
-    <row r="13" spans="2:32" s="4" customFormat="1" ht="61.95" customHeight="1">
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+    </row>
+    <row r="13" spans="2:36" s="4" customFormat="1" ht="61.95" customHeight="1">
       <c r="B13" s="38">
         <v>10</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="64" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="39" t="s">
@@ -1872,39 +2392,44 @@
       <c r="F13" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="40" t="s">
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="39" t="s">
+      <c r="K13" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="39"/>
-      <c r="L13" s="41">
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="41">
         <v>0</v>
       </c>
-      <c r="M13" s="42" t="s">
+      <c r="P13" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="N13" s="38" t="s">
+      <c r="Q13" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="O13" s="38" t="s">
+      <c r="R13" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-    </row>
-    <row r="14" spans="2:32" s="4" customFormat="1" ht="75">
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+    </row>
+    <row r="14" spans="2:36" s="4" customFormat="1" ht="75">
       <c r="B14" s="38">
         <v>11</v>
       </c>
-      <c r="C14" s="62"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="39" t="s">
         <v>84</v>
       </c>
@@ -1914,39 +2439,44 @@
       <c r="F14" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="44" t="s">
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="I14" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="39" t="s">
+      <c r="K14" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="39"/>
-      <c r="L14" s="41">
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="41">
         <v>0</v>
       </c>
-      <c r="M14" s="42" t="s">
+      <c r="P14" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="N14" s="38" t="s">
+      <c r="Q14" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="O14" s="38" t="s">
+      <c r="R14" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-    </row>
-    <row r="15" spans="2:32" s="2" customFormat="1" ht="75.599999999999994">
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+    </row>
+    <row r="15" spans="2:36" s="2" customFormat="1" ht="75.599999999999994">
       <c r="B15" s="22">
         <v>12</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="54" t="s">
         <v>88</v>
       </c>
       <c r="D15" s="23" t="s">
@@ -1958,38 +2488,38 @@
       <c r="F15" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="29" t="s">
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="23" t="s">
+      <c r="K15" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="K15" s="23"/>
-      <c r="L15" s="26">
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="26">
         <v>10</v>
       </c>
-      <c r="M15" s="27" t="s">
+      <c r="P15" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="N15" s="22" t="s">
+      <c r="Q15" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="O15" s="22" t="s">
+      <c r="R15" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
@@ -2000,12 +2530,16 @@
       <c r="AD15" s="11"/>
       <c r="AE15" s="11"/>
       <c r="AF15" s="11"/>
-    </row>
-    <row r="16" spans="2:32" s="2" customFormat="1" ht="90.6">
+      <c r="AG15" s="11"/>
+      <c r="AH15" s="11"/>
+      <c r="AI15" s="11"/>
+      <c r="AJ15" s="11"/>
+    </row>
+    <row r="16" spans="2:36" s="2" customFormat="1" ht="90.6">
       <c r="B16" s="22">
         <v>13</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="23" t="s">
         <v>95</v>
       </c>
@@ -2015,38 +2549,38 @@
       <c r="F16" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="29" t="s">
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I16" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="23" t="s">
+      <c r="K16" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K16" s="23"/>
-      <c r="L16" s="26">
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="26">
         <v>0</v>
       </c>
-      <c r="M16" s="27" t="s">
+      <c r="P16" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="N16" s="22" t="s">
+      <c r="Q16" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="O16" s="22" t="s">
+      <c r="R16" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
@@ -2057,12 +2591,16 @@
       <c r="AD16" s="11"/>
       <c r="AE16" s="11"/>
       <c r="AF16" s="11"/>
-    </row>
-    <row r="17" spans="2:32" s="2" customFormat="1" ht="75">
+      <c r="AG16" s="11"/>
+      <c r="AH16" s="11"/>
+      <c r="AI16" s="11"/>
+      <c r="AJ16" s="11"/>
+    </row>
+    <row r="17" spans="2:36" s="2" customFormat="1" ht="75">
       <c r="B17" s="22">
         <v>14</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="54" t="s">
         <v>99</v>
       </c>
       <c r="D17" s="23" t="s">
@@ -2074,39 +2612,44 @@
       <c r="F17" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="29" t="s">
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="23" t="s">
+      <c r="K17" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="23"/>
-      <c r="L17" s="26">
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="26">
         <v>30</v>
       </c>
-      <c r="M17" s="24" t="s">
+      <c r="P17" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="N17" s="38" t="s">
+      <c r="Q17" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="O17" s="22" t="s">
+      <c r="R17" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-    </row>
-    <row r="18" spans="2:32" s="2" customFormat="1" ht="60">
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="28"/>
+    </row>
+    <row r="18" spans="2:36" s="2" customFormat="1" ht="60">
       <c r="B18" s="22">
         <v>15</v>
       </c>
-      <c r="C18" s="63"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="23" t="s">
         <v>105</v>
       </c>
@@ -2116,39 +2659,44 @@
       <c r="F18" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="45" t="s">
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="I18" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="23" t="s">
+      <c r="K18" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="23"/>
-      <c r="L18" s="26">
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="26">
         <v>40</v>
       </c>
-      <c r="M18" s="24" t="s">
+      <c r="P18" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="N18" s="22" t="s">
+      <c r="Q18" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="O18" s="22" t="s">
+      <c r="R18" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-    </row>
-    <row r="19" spans="2:32" s="2" customFormat="1" ht="60">
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="28"/>
+    </row>
+    <row r="19" spans="2:36" s="2" customFormat="1" ht="60">
       <c r="B19" s="22">
         <v>16</v>
       </c>
-      <c r="C19" s="57"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="23" t="s">
         <v>109</v>
       </c>
@@ -2158,39 +2706,44 @@
       <c r="F19" s="46">
         <v>145938840</v>
       </c>
-      <c r="G19" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="45" t="s">
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="23" t="s">
+      <c r="K19" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="K19" s="23"/>
-      <c r="L19" s="26">
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="26">
         <v>50</v>
       </c>
-      <c r="M19" s="27" t="s">
+      <c r="P19" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="N19" s="22" t="s">
+      <c r="Q19" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="O19" s="22" t="s">
+      <c r="R19" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-    </row>
-    <row r="20" spans="2:32" s="3" customFormat="1" ht="60">
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+    </row>
+    <row r="20" spans="2:36" s="3" customFormat="1" ht="60">
       <c r="B20" s="32">
         <v>17</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="57" t="s">
         <v>115</v>
       </c>
       <c r="D20" s="33" t="s">
@@ -2202,38 +2755,38 @@
       <c r="F20" s="47">
         <v>96214685</v>
       </c>
-      <c r="G20" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="35" t="s">
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="I20" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="33" t="s">
+      <c r="K20" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="K20" s="33"/>
-      <c r="L20" s="26">
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="26">
         <v>0</v>
       </c>
-      <c r="M20" s="36" t="s">
+      <c r="P20" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="N20" s="32" t="s">
+      <c r="Q20" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="O20" s="32" t="s">
+      <c r="R20" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
+      <c r="S20" s="37"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="37"/>
+      <c r="V20" s="37"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
@@ -2244,12 +2797,16 @@
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
-    </row>
-    <row r="21" spans="2:32" s="3" customFormat="1" ht="90">
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="2"/>
+      <c r="AI20" s="2"/>
+      <c r="AJ20" s="2"/>
+    </row>
+    <row r="21" spans="2:36" s="3" customFormat="1" ht="90">
       <c r="B21" s="32">
         <v>18</v>
       </c>
-      <c r="C21" s="64"/>
+      <c r="C21" s="57"/>
       <c r="D21" s="33" t="s">
         <v>116</v>
       </c>
@@ -2259,38 +2816,38 @@
       <c r="F21" s="47">
         <v>91562164</v>
       </c>
-      <c r="G21" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="35" t="s">
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="33" t="s">
+      <c r="K21" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="33"/>
-      <c r="L21" s="26">
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="26">
         <v>0</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="P21" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="N21" s="32" t="s">
+      <c r="Q21" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="O21" s="32" t="s">
+      <c r="R21" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="37"/>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
@@ -2301,12 +2858,16 @@
       <c r="AD21" s="2"/>
       <c r="AE21" s="2"/>
       <c r="AF21" s="2"/>
-    </row>
-    <row r="22" spans="2:32" s="2" customFormat="1" ht="75">
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="2"/>
+      <c r="AI21" s="2"/>
+      <c r="AJ21" s="2"/>
+    </row>
+    <row r="22" spans="2:36" s="2" customFormat="1" ht="75">
       <c r="B22" s="22">
         <v>19</v>
       </c>
-      <c r="C22" s="65"/>
+      <c r="C22" s="58"/>
       <c r="D22" s="23" t="s">
         <v>125</v>
       </c>
@@ -2316,39 +2877,44 @@
       <c r="F22" s="46">
         <v>108295464</v>
       </c>
-      <c r="G22" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="29" t="s">
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="23" t="s">
+      <c r="K22" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="23"/>
-      <c r="L22" s="26">
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="26">
         <v>0</v>
       </c>
-      <c r="M22" s="27" t="s">
+      <c r="P22" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="N22" s="22" t="s">
+      <c r="Q22" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="O22" s="22" t="s">
+      <c r="R22" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-    </row>
-    <row r="23" spans="2:32" s="2" customFormat="1" ht="75">
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+    </row>
+    <row r="23" spans="2:36" s="2" customFormat="1" ht="75">
       <c r="B23" s="22">
         <v>20</v>
       </c>
-      <c r="C23" s="56" t="s">
+      <c r="C23" s="54" t="s">
         <v>130</v>
       </c>
       <c r="D23" s="23" t="s">
@@ -2360,39 +2926,44 @@
       <c r="F23" s="46">
         <v>140410915</v>
       </c>
-      <c r="G23" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="29" t="s">
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="I23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="23" t="s">
+      <c r="K23" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K23" s="23"/>
-      <c r="L23" s="26">
-        <v>20</v>
-      </c>
-      <c r="M23" s="27" t="s">
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="26">
+        <v>20</v>
+      </c>
+      <c r="P23" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="N23" s="22" t="s">
+      <c r="Q23" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="O23" s="22" t="s">
+      <c r="R23" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-    </row>
-    <row r="24" spans="2:32" s="2" customFormat="1" ht="120">
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+    </row>
+    <row r="24" spans="2:36" s="2" customFormat="1" ht="120">
       <c r="B24" s="22">
         <v>21</v>
       </c>
-      <c r="C24" s="57"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="23" t="s">
         <v>136</v>
       </c>
@@ -2402,39 +2973,44 @@
       <c r="F24" s="46">
         <v>246235000</v>
       </c>
-      <c r="G24" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="29" t="s">
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="23" t="s">
+      <c r="K24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K24" s="23"/>
-      <c r="L24" s="26">
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="26">
         <v>15</v>
       </c>
-      <c r="M24" s="27" t="s">
+      <c r="P24" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="N24" s="22" t="s">
+      <c r="Q24" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="O24" s="22" t="s">
+      <c r="R24" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-    </row>
-    <row r="25" spans="2:32" s="2" customFormat="1" ht="75">
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="28"/>
+    </row>
+    <row r="25" spans="2:36" s="2" customFormat="1" ht="75">
       <c r="B25" s="22">
         <v>22</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="54" t="s">
         <v>140</v>
       </c>
       <c r="D25" s="23" t="s">
@@ -2446,39 +3022,44 @@
       <c r="F25" s="46">
         <v>162382000</v>
       </c>
-      <c r="G25" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="29" t="s">
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I25" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="23" t="s">
+      <c r="K25" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K25" s="23"/>
-      <c r="L25" s="26">
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="26">
         <v>0</v>
       </c>
-      <c r="M25" s="27" t="s">
+      <c r="P25" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="N25" s="22" t="s">
+      <c r="Q25" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="O25" s="22" t="s">
+      <c r="R25" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-    </row>
-    <row r="26" spans="2:32" s="2" customFormat="1" ht="60">
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="28"/>
+    </row>
+    <row r="26" spans="2:36" s="2" customFormat="1" ht="60">
       <c r="B26" s="22">
         <v>23</v>
       </c>
-      <c r="C26" s="57"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="23" t="s">
         <v>145</v>
       </c>
@@ -2488,39 +3069,44 @@
       <c r="F26" s="46">
         <v>159222422</v>
       </c>
-      <c r="G26" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="29" t="s">
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="23" t="s">
+      <c r="K26" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K26" s="23"/>
-      <c r="L26" s="26">
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="26">
         <v>0</v>
       </c>
-      <c r="M26" s="27" t="s">
+      <c r="P26" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="N26" s="22" t="s">
+      <c r="Q26" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="O26" s="22" t="s">
+      <c r="R26" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-    </row>
-    <row r="27" spans="2:32" s="3" customFormat="1" ht="60">
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+    </row>
+    <row r="27" spans="2:36" s="3" customFormat="1" ht="60">
       <c r="B27" s="22">
         <v>24</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="54" t="s">
         <v>148</v>
       </c>
       <c r="D27" s="23" t="s">
@@ -2532,36 +3118,36 @@
       <c r="F27" s="46">
         <v>193740000</v>
       </c>
-      <c r="G27" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="29" t="s">
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="26">
+      <c r="K27" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="26">
         <v>0</v>
       </c>
-      <c r="M27" s="27" t="s">
+      <c r="P27" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="N27" s="22" t="s">
+      <c r="Q27" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="O27" s="22" t="s">
+      <c r="R27" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
@@ -2572,12 +3158,16 @@
       <c r="AD27" s="2"/>
       <c r="AE27" s="2"/>
       <c r="AF27" s="2"/>
-    </row>
-    <row r="28" spans="2:32" s="2" customFormat="1" ht="105">
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+    </row>
+    <row r="28" spans="2:36" s="2" customFormat="1" ht="105">
       <c r="B28" s="22">
         <v>25</v>
       </c>
-      <c r="C28" s="63"/>
+      <c r="C28" s="55"/>
       <c r="D28" s="23" t="s">
         <v>154</v>
       </c>
@@ -2587,39 +3177,44 @@
       <c r="F28" s="46">
         <v>147335706</v>
       </c>
-      <c r="G28" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="29" t="s">
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="23" t="s">
+      <c r="K28" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K28" s="23"/>
-      <c r="L28" s="26">
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="26">
         <v>0</v>
       </c>
-      <c r="M28" s="27" t="s">
+      <c r="P28" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="N28" s="22" t="s">
+      <c r="Q28" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="O28" s="22" t="s">
+      <c r="R28" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-    </row>
-    <row r="29" spans="2:32" s="2" customFormat="1" ht="60">
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+    </row>
+    <row r="29" spans="2:36" s="2" customFormat="1" ht="60">
       <c r="B29" s="22">
         <v>26</v>
       </c>
-      <c r="C29" s="57"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="23" t="s">
         <v>154</v>
       </c>
@@ -2629,35 +3224,40 @@
       <c r="F29" s="46">
         <v>118575500</v>
       </c>
-      <c r="G29" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="29" t="s">
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="23" t="s">
+      <c r="K29" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K29" s="23"/>
-      <c r="L29" s="26">
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="26">
         <v>0</v>
       </c>
-      <c r="M29" s="27" t="s">
+      <c r="P29" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="N29" s="22" t="s">
+      <c r="Q29" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="O29" s="22" t="s">
+      <c r="R29" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-    </row>
-    <row r="30" spans="2:32" s="5" customFormat="1" ht="78" customHeight="1">
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+    </row>
+    <row r="30" spans="2:36" s="5" customFormat="1" ht="78" customHeight="1">
       <c r="B30" s="48"/>
       <c r="C30" s="48" t="s">
         <v>159</v>
@@ -2665,24 +3265,25 @@
       <c r="D30" s="48"/>
       <c r="E30" s="49"/>
       <c r="F30" s="50"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="51"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
       <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
+      <c r="J30" s="51"/>
       <c r="K30" s="49"/>
-      <c r="L30" s="52">
-        <v>6.73</v>
-      </c>
-      <c r="M30" s="48"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="53"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="53"/>
-      <c r="V30" s="53"/>
+      <c r="L30" s="49"/>
+      <c r="M30" s="49"/>
+      <c r="N30" s="49"/>
+      <c r="O30" s="52">
+        <f>AVERAGE(O4:O29)</f>
+        <v>6.35</v>
+      </c>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="51"/>
+      <c r="T30" s="51"/>
+      <c r="U30" s="51"/>
+      <c r="V30" s="51"/>
       <c r="W30" s="53"/>
       <c r="X30" s="53"/>
       <c r="Y30" s="53"/>
@@ -2693,625 +3294,6818 @@
       <c r="AD30" s="53"/>
       <c r="AE30" s="53"/>
       <c r="AF30" s="53"/>
-    </row>
-    <row r="31" spans="2:32">
+      <c r="AG30" s="53"/>
+      <c r="AH30" s="53"/>
+      <c r="AI30" s="53"/>
+      <c r="AJ30" s="53"/>
+    </row>
+    <row r="31" spans="2:36">
       <c r="B31" s="13"/>
       <c r="C31" s="14"/>
       <c r="D31" s="13"/>
       <c r="E31" s="12"/>
       <c r="F31" s="15"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
+      <c r="J31" s="11"/>
       <c r="K31" s="12"/>
       <c r="L31" s="12"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-    </row>
-    <row r="32" spans="2:32">
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="11"/>
+    </row>
+    <row r="32" spans="2:36">
       <c r="B32" s="13"/>
       <c r="C32" s="14"/>
       <c r="D32" s="13"/>
       <c r="E32" s="12"/>
       <c r="F32" s="15"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="11"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
+      <c r="J32" s="11"/>
       <c r="K32" s="12"/>
       <c r="L32" s="12"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-    </row>
-    <row r="33" spans="2:17">
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+    </row>
+    <row r="33" spans="2:21">
       <c r="B33" s="13"/>
       <c r="C33" s="14"/>
       <c r="D33" s="13"/>
       <c r="E33" s="12"/>
       <c r="F33" s="15"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="11"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
+      <c r="J33" s="11"/>
       <c r="K33" s="12"/>
       <c r="L33" s="12"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-    </row>
-    <row r="34" spans="2:17">
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="11"/>
+    </row>
+    <row r="34" spans="2:21">
       <c r="B34" s="13"/>
       <c r="C34" s="14"/>
       <c r="D34" s="13"/>
       <c r="E34" s="12"/>
       <c r="F34" s="15"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="11"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
+      <c r="J34" s="11"/>
       <c r="K34" s="12"/>
       <c r="L34" s="12"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
-    </row>
-    <row r="35" spans="2:17">
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+    </row>
+    <row r="35" spans="2:21">
       <c r="B35" s="13"/>
       <c r="C35" s="14"/>
       <c r="D35" s="13"/>
       <c r="E35" s="12"/>
       <c r="F35" s="15"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
+      <c r="J35" s="11"/>
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-    </row>
-    <row r="36" spans="2:17">
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+    </row>
+    <row r="36" spans="2:21">
       <c r="B36" s="13"/>
       <c r="C36" s="14"/>
       <c r="D36" s="13"/>
       <c r="E36" s="12"/>
       <c r="F36" s="15"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="11"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
       <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
+      <c r="J36" s="11"/>
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
-    </row>
-    <row r="37" spans="2:17">
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="11"/>
+    </row>
+    <row r="37" spans="2:21">
       <c r="B37" s="13"/>
       <c r="C37" s="14"/>
       <c r="D37" s="13"/>
       <c r="E37" s="12"/>
       <c r="F37" s="15"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="11"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
       <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
+      <c r="J37" s="11"/>
       <c r="K37" s="12"/>
       <c r="L37" s="12"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
-    </row>
-    <row r="38" spans="2:17">
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="11"/>
+    </row>
+    <row r="38" spans="2:21">
       <c r="B38" s="13"/>
       <c r="C38" s="14"/>
       <c r="D38" s="13"/>
       <c r="E38" s="12"/>
       <c r="F38" s="15"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="11"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
       <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
+      <c r="J38" s="11"/>
       <c r="K38" s="12"/>
       <c r="L38" s="12"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
-    </row>
-    <row r="39" spans="2:17">
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+    </row>
+    <row r="39" spans="2:21">
       <c r="B39" s="13"/>
       <c r="C39" s="14"/>
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>
       <c r="F39" s="15"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
       <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
+      <c r="J39" s="11"/>
       <c r="K39" s="12"/>
       <c r="L39" s="12"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11"/>
-    </row>
-    <row r="40" spans="2:17">
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="12"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="11"/>
+    </row>
+    <row r="40" spans="2:21">
       <c r="B40" s="13"/>
       <c r="C40" s="14"/>
       <c r="D40" s="13"/>
       <c r="E40" s="12"/>
       <c r="F40" s="15"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="11"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
       <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
+      <c r="J40" s="11"/>
       <c r="K40" s="12"/>
       <c r="L40" s="12"/>
-      <c r="M40" s="13"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11"/>
-    </row>
-    <row r="41" spans="2:17">
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="11"/>
+    </row>
+    <row r="41" spans="2:21">
       <c r="B41" s="13"/>
       <c r="C41" s="14"/>
       <c r="D41" s="13"/>
       <c r="E41" s="12"/>
       <c r="F41" s="15"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="11"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
       <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
+      <c r="J41" s="11"/>
       <c r="K41" s="12"/>
       <c r="L41" s="12"/>
-      <c r="M41" s="13"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-    </row>
-    <row r="42" spans="2:17">
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+    </row>
+    <row r="42" spans="2:21">
       <c r="B42" s="13"/>
       <c r="C42" s="14"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
       <c r="F42" s="15"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="11"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
       <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
+      <c r="J42" s="11"/>
       <c r="K42" s="12"/>
       <c r="L42" s="12"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
-    </row>
-    <row r="43" spans="2:17">
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="12"/>
+      <c r="P42" s="13"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="11"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="11"/>
+    </row>
+    <row r="43" spans="2:21">
       <c r="B43" s="13"/>
       <c r="C43" s="14"/>
       <c r="D43" s="13"/>
       <c r="E43" s="12"/>
       <c r="F43" s="15"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="11"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
       <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
+      <c r="J43" s="11"/>
       <c r="K43" s="12"/>
       <c r="L43" s="12"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-    </row>
-    <row r="44" spans="2:17">
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="15"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="11"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="11"/>
+    </row>
+    <row r="44" spans="2:21">
       <c r="B44" s="13"/>
       <c r="C44" s="14"/>
       <c r="D44" s="13"/>
       <c r="E44" s="12"/>
       <c r="F44" s="15"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="11"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
       <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
+      <c r="J44" s="11"/>
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="15"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="11"/>
-    </row>
-    <row r="45" spans="2:17">
-      <c r="L45" s="12"/>
-    </row>
-    <row r="46" spans="2:17">
-      <c r="L46" s="12"/>
-    </row>
-    <row r="47" spans="2:17">
-      <c r="L47" s="12"/>
-    </row>
-    <row r="48" spans="2:17">
-      <c r="L48" s="12"/>
-    </row>
-    <row r="49" spans="12:12">
-      <c r="L49" s="12"/>
-    </row>
-    <row r="50" spans="12:12">
-      <c r="L50" s="12"/>
-    </row>
-    <row r="51" spans="12:12">
-      <c r="L51" s="12"/>
-    </row>
-    <row r="52" spans="12:12">
-      <c r="L52" s="12"/>
-    </row>
-    <row r="53" spans="12:12">
-      <c r="L53" s="12"/>
-    </row>
-    <row r="54" spans="12:12">
-      <c r="L54" s="12"/>
-    </row>
-    <row r="55" spans="12:12">
-      <c r="L55" s="12"/>
-    </row>
-    <row r="56" spans="12:12">
-      <c r="L56" s="12"/>
-    </row>
-    <row r="57" spans="12:12">
-      <c r="L57" s="12"/>
-    </row>
-    <row r="58" spans="12:12">
-      <c r="L58" s="12"/>
-    </row>
-    <row r="59" spans="12:12">
-      <c r="L59" s="12"/>
-    </row>
-    <row r="60" spans="12:12">
-      <c r="L60" s="12"/>
-    </row>
-    <row r="61" spans="12:12">
-      <c r="L61" s="12"/>
-    </row>
-    <row r="62" spans="12:12">
-      <c r="L62" s="12"/>
-    </row>
-    <row r="63" spans="12:12">
-      <c r="L63" s="12"/>
-    </row>
-    <row r="64" spans="12:12">
-      <c r="L64" s="12"/>
-    </row>
-    <row r="65" spans="12:12">
-      <c r="L65" s="12"/>
-    </row>
-    <row r="66" spans="12:12">
-      <c r="L66" s="12"/>
-    </row>
-    <row r="67" spans="12:12">
-      <c r="L67" s="12"/>
-    </row>
-    <row r="68" spans="12:12">
-      <c r="L68" s="12"/>
-    </row>
-    <row r="69" spans="12:12">
-      <c r="L69" s="12"/>
-    </row>
-    <row r="70" spans="12:12">
-      <c r="L70" s="12"/>
-    </row>
-    <row r="71" spans="12:12">
-      <c r="L71" s="12"/>
-    </row>
-    <row r="72" spans="12:12">
-      <c r="L72" s="12"/>
-    </row>
-    <row r="73" spans="12:12">
-      <c r="L73" s="12"/>
-    </row>
-    <row r="74" spans="12:12">
-      <c r="L74" s="12"/>
-    </row>
-    <row r="75" spans="12:12">
-      <c r="L75" s="12"/>
-    </row>
-    <row r="76" spans="12:12">
-      <c r="L76" s="12"/>
-    </row>
-    <row r="77" spans="12:12">
-      <c r="L77" s="12"/>
-    </row>
-    <row r="78" spans="12:12">
-      <c r="L78" s="12"/>
-    </row>
-    <row r="79" spans="12:12">
-      <c r="L79" s="12"/>
-    </row>
-    <row r="80" spans="12:12">
-      <c r="L80" s="12"/>
-    </row>
-    <row r="81" spans="12:12">
-      <c r="L81" s="12"/>
-    </row>
-    <row r="82" spans="12:12">
-      <c r="L82" s="12"/>
-    </row>
-    <row r="83" spans="12:12">
-      <c r="L83" s="12"/>
-    </row>
-    <row r="84" spans="12:12">
-      <c r="L84" s="12"/>
-    </row>
-    <row r="85" spans="12:12">
-      <c r="L85" s="12"/>
-    </row>
-    <row r="86" spans="12:12">
-      <c r="L86" s="12"/>
-    </row>
-    <row r="87" spans="12:12">
-      <c r="L87" s="12"/>
-    </row>
-    <row r="88" spans="12:12">
-      <c r="L88" s="12"/>
-    </row>
-    <row r="89" spans="12:12">
-      <c r="L89" s="12"/>
-    </row>
-    <row r="90" spans="12:12">
-      <c r="L90" s="12"/>
-    </row>
-    <row r="91" spans="12:12">
-      <c r="L91" s="12"/>
-    </row>
-    <row r="92" spans="12:12">
-      <c r="L92" s="12"/>
-    </row>
-    <row r="93" spans="12:12">
-      <c r="L93" s="12"/>
-    </row>
-    <row r="94" spans="12:12">
-      <c r="L94" s="12"/>
-    </row>
-    <row r="95" spans="12:12">
-      <c r="L95" s="12"/>
-    </row>
-    <row r="96" spans="12:12">
-      <c r="L96" s="12"/>
-    </row>
-    <row r="97" spans="12:12">
-      <c r="L97" s="12"/>
-    </row>
-    <row r="98" spans="12:12">
-      <c r="L98" s="12"/>
-    </row>
-    <row r="99" spans="12:12">
-      <c r="L99" s="12"/>
-    </row>
-    <row r="100" spans="12:12">
-      <c r="L100" s="12"/>
-    </row>
-    <row r="101" spans="12:12">
-      <c r="L101" s="12"/>
-    </row>
-    <row r="102" spans="12:12">
-      <c r="L102" s="12"/>
-    </row>
-    <row r="103" spans="12:12">
-      <c r="L103" s="12"/>
-    </row>
-    <row r="104" spans="12:12">
-      <c r="L104" s="12"/>
-    </row>
-    <row r="105" spans="12:12">
-      <c r="L105" s="12"/>
-    </row>
-    <row r="106" spans="12:12">
-      <c r="L106" s="12"/>
-    </row>
-    <row r="107" spans="12:12">
-      <c r="L107" s="12"/>
-    </row>
-    <row r="108" spans="12:12">
-      <c r="L108" s="12"/>
-    </row>
-    <row r="109" spans="12:12">
-      <c r="L109" s="12"/>
-    </row>
-    <row r="110" spans="12:12">
-      <c r="L110" s="12"/>
-    </row>
-    <row r="111" spans="12:12">
-      <c r="L111" s="12"/>
-    </row>
-    <row r="112" spans="12:12">
-      <c r="L112" s="12"/>
-    </row>
-    <row r="113" spans="12:12">
-      <c r="L113" s="12"/>
-    </row>
-    <row r="114" spans="12:12">
-      <c r="L114" s="12"/>
-    </row>
-    <row r="115" spans="12:12">
-      <c r="L115" s="12"/>
-    </row>
-    <row r="116" spans="12:12">
-      <c r="L116" s="12"/>
-    </row>
-    <row r="117" spans="12:12">
-      <c r="L117" s="12"/>
-    </row>
-    <row r="118" spans="12:12">
-      <c r="L118" s="12"/>
-    </row>
-    <row r="119" spans="12:12">
-      <c r="L119" s="12"/>
-    </row>
-    <row r="120" spans="12:12">
-      <c r="L120" s="12"/>
-    </row>
-    <row r="121" spans="12:12">
-      <c r="L121" s="12"/>
-    </row>
-    <row r="122" spans="12:12">
-      <c r="L122" s="12"/>
-    </row>
-    <row r="123" spans="12:12">
-      <c r="L123" s="12"/>
-    </row>
-    <row r="124" spans="12:12">
-      <c r="L124" s="12"/>
-    </row>
-    <row r="125" spans="12:12">
-      <c r="L125" s="12"/>
-    </row>
-    <row r="126" spans="12:12">
-      <c r="L126" s="12"/>
-    </row>
-    <row r="127" spans="12:12">
-      <c r="L127" s="12"/>
-    </row>
-    <row r="128" spans="12:12">
-      <c r="L128" s="12"/>
-    </row>
-    <row r="129" spans="12:12">
-      <c r="L129" s="12"/>
-    </row>
-    <row r="130" spans="12:12">
-      <c r="L130" s="12"/>
-    </row>
-    <row r="131" spans="12:12">
-      <c r="L131" s="12"/>
-    </row>
-    <row r="132" spans="12:12">
-      <c r="L132" s="12"/>
-    </row>
-    <row r="133" spans="12:12">
-      <c r="L133" s="12"/>
-    </row>
-    <row r="134" spans="12:12">
-      <c r="L134" s="12"/>
-    </row>
-    <row r="135" spans="12:12">
-      <c r="L135" s="12"/>
-    </row>
-    <row r="136" spans="12:12">
-      <c r="L136" s="12"/>
-    </row>
-    <row r="137" spans="12:12">
-      <c r="L137" s="12"/>
-    </row>
-    <row r="138" spans="12:12">
-      <c r="L138" s="12"/>
-    </row>
-    <row r="139" spans="12:12">
-      <c r="L139" s="12"/>
-    </row>
-    <row r="140" spans="12:12">
-      <c r="L140" s="12"/>
-    </row>
-    <row r="141" spans="12:12">
-      <c r="L141" s="12"/>
-    </row>
-    <row r="142" spans="12:12">
-      <c r="L142" s="12"/>
-    </row>
-    <row r="143" spans="12:12">
-      <c r="L143" s="12"/>
-    </row>
-    <row r="144" spans="12:12">
-      <c r="L144" s="12"/>
-    </row>
-    <row r="145" spans="12:12">
-      <c r="L145" s="12"/>
-    </row>
-    <row r="146" spans="12:12">
-      <c r="L146" s="12"/>
-    </row>
-    <row r="147" spans="12:12">
-      <c r="L147" s="12"/>
-    </row>
-    <row r="148" spans="12:12">
-      <c r="L148" s="12"/>
-    </row>
-    <row r="149" spans="12:12">
-      <c r="L149" s="12"/>
-    </row>
-    <row r="150" spans="12:12">
-      <c r="L150" s="12"/>
-    </row>
-    <row r="151" spans="12:12">
-      <c r="L151" s="12"/>
-    </row>
-    <row r="152" spans="12:12">
-      <c r="L152" s="12"/>
-    </row>
-    <row r="153" spans="12:12">
-      <c r="L153" s="12"/>
-    </row>
-    <row r="154" spans="12:12">
-      <c r="L154" s="12"/>
-    </row>
-    <row r="155" spans="12:12">
-      <c r="L155" s="12"/>
-    </row>
-    <row r="156" spans="12:12">
-      <c r="L156" s="12"/>
-    </row>
-    <row r="157" spans="12:12">
-      <c r="L157" s="12"/>
-    </row>
-    <row r="158" spans="12:12">
-      <c r="L158" s="12"/>
-    </row>
-    <row r="159" spans="12:12">
-      <c r="L159" s="12"/>
-    </row>
-    <row r="160" spans="12:12">
-      <c r="L160" s="12"/>
-    </row>
-    <row r="161" spans="12:12">
-      <c r="L161" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="12"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="15"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="11"/>
+      <c r="U44" s="11"/>
+    </row>
+    <row r="45" spans="2:21">
+      <c r="O45" s="12"/>
+    </row>
+    <row r="46" spans="2:21">
+      <c r="O46" s="12"/>
+    </row>
+    <row r="47" spans="2:21">
+      <c r="O47" s="12"/>
+    </row>
+    <row r="48" spans="2:21">
+      <c r="O48" s="12"/>
+    </row>
+    <row r="49" spans="15:15">
+      <c r="O49" s="12"/>
+    </row>
+    <row r="50" spans="15:15">
+      <c r="O50" s="12"/>
+    </row>
+    <row r="51" spans="15:15">
+      <c r="O51" s="12"/>
+    </row>
+    <row r="52" spans="15:15">
+      <c r="O52" s="12"/>
+    </row>
+    <row r="53" spans="15:15">
+      <c r="O53" s="12"/>
+    </row>
+    <row r="54" spans="15:15">
+      <c r="O54" s="12"/>
+    </row>
+    <row r="55" spans="15:15">
+      <c r="O55" s="12"/>
+    </row>
+    <row r="56" spans="15:15">
+      <c r="O56" s="12"/>
+    </row>
+    <row r="57" spans="15:15">
+      <c r="O57" s="12"/>
+    </row>
+    <row r="58" spans="15:15">
+      <c r="O58" s="12"/>
+    </row>
+    <row r="59" spans="15:15">
+      <c r="O59" s="12"/>
+    </row>
+    <row r="60" spans="15:15">
+      <c r="O60" s="12"/>
+    </row>
+    <row r="61" spans="15:15">
+      <c r="O61" s="12"/>
+    </row>
+    <row r="62" spans="15:15">
+      <c r="O62" s="12"/>
+    </row>
+    <row r="63" spans="15:15">
+      <c r="O63" s="12"/>
+    </row>
+    <row r="64" spans="15:15">
+      <c r="O64" s="12"/>
+    </row>
+    <row r="65" spans="15:15">
+      <c r="O65" s="12"/>
+    </row>
+    <row r="66" spans="15:15">
+      <c r="O66" s="12"/>
+    </row>
+    <row r="67" spans="15:15">
+      <c r="O67" s="12"/>
+    </row>
+    <row r="68" spans="15:15">
+      <c r="O68" s="12"/>
+    </row>
+    <row r="69" spans="15:15">
+      <c r="O69" s="12"/>
+    </row>
+    <row r="70" spans="15:15">
+      <c r="O70" s="12"/>
+    </row>
+    <row r="71" spans="15:15">
+      <c r="O71" s="12"/>
+    </row>
+    <row r="72" spans="15:15">
+      <c r="O72" s="12"/>
+    </row>
+    <row r="73" spans="15:15">
+      <c r="O73" s="12"/>
+    </row>
+    <row r="74" spans="15:15">
+      <c r="O74" s="12"/>
+    </row>
+    <row r="75" spans="15:15">
+      <c r="O75" s="12"/>
+    </row>
+    <row r="76" spans="15:15">
+      <c r="O76" s="12"/>
+    </row>
+    <row r="77" spans="15:15">
+      <c r="O77" s="12"/>
+    </row>
+    <row r="78" spans="15:15">
+      <c r="O78" s="12"/>
+    </row>
+    <row r="79" spans="15:15">
+      <c r="O79" s="12"/>
+    </row>
+    <row r="80" spans="15:15">
+      <c r="O80" s="12"/>
+    </row>
+    <row r="81" spans="15:15">
+      <c r="O81" s="12"/>
+    </row>
+    <row r="82" spans="15:15">
+      <c r="O82" s="12"/>
+    </row>
+    <row r="83" spans="15:15">
+      <c r="O83" s="12"/>
+    </row>
+    <row r="84" spans="15:15">
+      <c r="O84" s="12"/>
+    </row>
+    <row r="85" spans="15:15">
+      <c r="O85" s="12"/>
+    </row>
+    <row r="86" spans="15:15">
+      <c r="O86" s="12"/>
+    </row>
+    <row r="87" spans="15:15">
+      <c r="O87" s="12"/>
+    </row>
+    <row r="88" spans="15:15">
+      <c r="O88" s="12"/>
+    </row>
+    <row r="89" spans="15:15">
+      <c r="O89" s="12"/>
+    </row>
+    <row r="90" spans="15:15">
+      <c r="O90" s="12"/>
+    </row>
+    <row r="91" spans="15:15">
+      <c r="O91" s="12"/>
+    </row>
+    <row r="92" spans="15:15">
+      <c r="O92" s="12"/>
+    </row>
+    <row r="93" spans="15:15">
+      <c r="O93" s="12"/>
+    </row>
+    <row r="94" spans="15:15">
+      <c r="O94" s="12"/>
+    </row>
+    <row r="95" spans="15:15">
+      <c r="O95" s="12"/>
+    </row>
+    <row r="96" spans="15:15">
+      <c r="O96" s="12"/>
+    </row>
+    <row r="97" spans="15:15">
+      <c r="O97" s="12"/>
+    </row>
+    <row r="98" spans="15:15">
+      <c r="O98" s="12"/>
+    </row>
+    <row r="99" spans="15:15">
+      <c r="O99" s="12"/>
+    </row>
+    <row r="100" spans="15:15">
+      <c r="O100" s="12"/>
+    </row>
+    <row r="101" spans="15:15">
+      <c r="O101" s="12"/>
+    </row>
+    <row r="102" spans="15:15">
+      <c r="O102" s="12"/>
+    </row>
+    <row r="103" spans="15:15">
+      <c r="O103" s="12"/>
+    </row>
+    <row r="104" spans="15:15">
+      <c r="O104" s="12"/>
+    </row>
+    <row r="105" spans="15:15">
+      <c r="O105" s="12"/>
+    </row>
+    <row r="106" spans="15:15">
+      <c r="O106" s="12"/>
+    </row>
+    <row r="107" spans="15:15">
+      <c r="O107" s="12"/>
+    </row>
+    <row r="108" spans="15:15">
+      <c r="O108" s="12"/>
+    </row>
+    <row r="109" spans="15:15">
+      <c r="O109" s="12"/>
+    </row>
+    <row r="110" spans="15:15">
+      <c r="O110" s="12"/>
+    </row>
+    <row r="111" spans="15:15">
+      <c r="O111" s="12"/>
+    </row>
+    <row r="112" spans="15:15">
+      <c r="O112" s="12"/>
+    </row>
+    <row r="113" spans="15:15">
+      <c r="O113" s="12"/>
+    </row>
+    <row r="114" spans="15:15">
+      <c r="O114" s="12"/>
+    </row>
+    <row r="115" spans="15:15">
+      <c r="O115" s="12"/>
+    </row>
+    <row r="116" spans="15:15">
+      <c r="O116" s="12"/>
+    </row>
+    <row r="117" spans="15:15">
+      <c r="O117" s="12"/>
+    </row>
+    <row r="118" spans="15:15">
+      <c r="O118" s="12"/>
+    </row>
+    <row r="119" spans="15:15">
+      <c r="O119" s="12"/>
+    </row>
+    <row r="120" spans="15:15">
+      <c r="O120" s="12"/>
+    </row>
+    <row r="121" spans="15:15">
+      <c r="O121" s="12"/>
+    </row>
+    <row r="122" spans="15:15">
+      <c r="O122" s="12"/>
+    </row>
+    <row r="123" spans="15:15">
+      <c r="O123" s="12"/>
+    </row>
+    <row r="124" spans="15:15">
+      <c r="O124" s="12"/>
+    </row>
+    <row r="125" spans="15:15">
+      <c r="O125" s="12"/>
+    </row>
+    <row r="126" spans="15:15">
+      <c r="O126" s="12"/>
+    </row>
+    <row r="127" spans="15:15">
+      <c r="O127" s="12"/>
+    </row>
+    <row r="128" spans="15:15">
+      <c r="O128" s="12"/>
+    </row>
+    <row r="129" spans="15:15">
+      <c r="O129" s="12"/>
+    </row>
+    <row r="130" spans="15:15">
+      <c r="O130" s="12"/>
+    </row>
+    <row r="131" spans="15:15">
+      <c r="O131" s="12"/>
+    </row>
+    <row r="132" spans="15:15">
+      <c r="O132" s="12"/>
+    </row>
+    <row r="133" spans="15:15">
+      <c r="O133" s="12"/>
+    </row>
+    <row r="134" spans="15:15">
+      <c r="O134" s="12"/>
+    </row>
+    <row r="135" spans="15:15">
+      <c r="O135" s="12"/>
+    </row>
+    <row r="136" spans="15:15">
+      <c r="O136" s="12"/>
+    </row>
+    <row r="137" spans="15:15">
+      <c r="O137" s="12"/>
+    </row>
+    <row r="138" spans="15:15">
+      <c r="O138" s="12"/>
+    </row>
+    <row r="139" spans="15:15">
+      <c r="O139" s="12"/>
+    </row>
+    <row r="140" spans="15:15">
+      <c r="O140" s="12"/>
+    </row>
+    <row r="141" spans="15:15">
+      <c r="O141" s="12"/>
+    </row>
+    <row r="142" spans="15:15">
+      <c r="O142" s="12"/>
+    </row>
+    <row r="143" spans="15:15">
+      <c r="O143" s="12"/>
+    </row>
+    <row r="144" spans="15:15">
+      <c r="O144" s="12"/>
+    </row>
+    <row r="145" spans="15:15">
+      <c r="O145" s="12"/>
+    </row>
+    <row r="146" spans="15:15">
+      <c r="O146" s="12"/>
+    </row>
+    <row r="147" spans="15:15">
+      <c r="O147" s="12"/>
+    </row>
+    <row r="148" spans="15:15">
+      <c r="O148" s="12"/>
+    </row>
+    <row r="149" spans="15:15">
+      <c r="O149" s="12"/>
+    </row>
+    <row r="150" spans="15:15">
+      <c r="O150" s="12"/>
+    </row>
+    <row r="151" spans="15:15">
+      <c r="O151" s="12"/>
+    </row>
+    <row r="152" spans="15:15">
+      <c r="O152" s="12"/>
+    </row>
+    <row r="153" spans="15:15">
+      <c r="O153" s="12"/>
+    </row>
+    <row r="154" spans="15:15">
+      <c r="O154" s="12"/>
+    </row>
+    <row r="155" spans="15:15">
+      <c r="O155" s="12"/>
+    </row>
+    <row r="156" spans="15:15">
+      <c r="O156" s="12"/>
+    </row>
+    <row r="157" spans="15:15">
+      <c r="O157" s="12"/>
+    </row>
+    <row r="158" spans="15:15">
+      <c r="O158" s="12"/>
+    </row>
+    <row r="159" spans="15:15">
+      <c r="O159" s="12"/>
+    </row>
+    <row r="160" spans="15:15">
+      <c r="O160" s="12"/>
+    </row>
+    <row r="161" spans="15:15">
+      <c r="O161" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="C27:C29"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51F981B-3DC9-44AC-83BA-C6384E8B0665}">
+  <dimension ref="A1:R127"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" style="70" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="22.88671875" customWidth="1"/>
+    <col min="11" max="12" width="17.44140625" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" customWidth="1"/>
+    <col min="14" max="14" width="21.33203125" customWidth="1"/>
+    <col min="15" max="15" width="20.77734375" customWidth="1"/>
+    <col min="16" max="16" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.21875" customWidth="1"/>
+    <col min="18" max="18" width="20.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="62.4">
+      <c r="A1" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="69" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="66" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="69" t="s">
+        <v>164</v>
+      </c>
+      <c r="M1" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="69" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" customHeight="1">
+      <c r="A2" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G2" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="68" t="s">
+        <v>167</v>
+      </c>
+      <c r="I2" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L2" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="O2" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="P2" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+    </row>
+    <row r="3" spans="1:18" ht="15" customHeight="1">
+      <c r="A3" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G3" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L3" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="O3" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="P3" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+    </row>
+    <row r="4" spans="1:18" ht="30" customHeight="1">
+      <c r="A4" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="68" t="s">
+        <v>273</v>
+      </c>
+      <c r="I4" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L4" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="O4" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="P4" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q4" s="68"/>
+      <c r="R4" s="68"/>
+    </row>
+    <row r="5" spans="1:18" ht="15" customHeight="1">
+      <c r="A5" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G5" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L5" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="O5" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="P5" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+    </row>
+    <row r="6" spans="1:18" ht="15" customHeight="1">
+      <c r="A6" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G6" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="68" t="s">
+        <v>274</v>
+      </c>
+      <c r="I6" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L6" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="O6" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="P6" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+    </row>
+    <row r="7" spans="1:18" ht="15" customHeight="1">
+      <c r="A7" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G7" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="68" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O7" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="68"/>
+      <c r="R7" s="68"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" customHeight="1">
+      <c r="A8" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O8" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" customHeight="1">
+      <c r="A9" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="I9" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M9" s="68"/>
+      <c r="N9" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O9" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="68"/>
+      <c r="R9" s="68"/>
+    </row>
+    <row r="10" spans="1:18" ht="15" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G10" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O10" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="68"/>
+    </row>
+    <row r="11" spans="1:18" ht="15" customHeight="1">
+      <c r="A11" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G11" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O11" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P11" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="68"/>
+      <c r="R11" s="68"/>
+    </row>
+    <row r="12" spans="1:18" ht="15" customHeight="1">
+      <c r="A12" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="I12" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O12" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+    </row>
+    <row r="13" spans="1:18" ht="15" customHeight="1">
+      <c r="A13" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="68" t="s">
+        <v>176</v>
+      </c>
+      <c r="I13" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O13" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q13" s="68"/>
+      <c r="R13" s="68"/>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1">
+      <c r="A14" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="I14" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L14" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O14" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1">
+      <c r="A15" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F15" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G15" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="68" t="s">
+        <v>276</v>
+      </c>
+      <c r="I15" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L15" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O15" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q15" s="68"/>
+      <c r="R15" s="68"/>
+    </row>
+    <row r="16" spans="1:18" ht="15" customHeight="1">
+      <c r="A16" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F16" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G16" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L16" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M16" s="68"/>
+      <c r="N16" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O16" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P16" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="68"/>
+      <c r="R16" s="68"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1">
+      <c r="A17" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F17" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L17" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O17" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P17" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="68"/>
+      <c r="R17" s="68"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1">
+      <c r="A18" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G18" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K18" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L18" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M18" s="68"/>
+      <c r="N18" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O18" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q18" s="68"/>
+      <c r="R18" s="68"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1">
+      <c r="A19" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F19" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G19" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="I19" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K19" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L19" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O19" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="P19" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" customHeight="1">
+      <c r="A20" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="I20" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K20" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L20" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O20" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="P20" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="68"/>
+      <c r="R20" s="68"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" customHeight="1">
+      <c r="A21" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F21" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G21" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>182</v>
+      </c>
+      <c r="I21" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K21" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L21" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O21" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="P21" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="68"/>
+      <c r="R21" s="68"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" customHeight="1">
+      <c r="A22" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F22" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G22" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="I22" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K22" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L22" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O22" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="P22" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="68"/>
+      <c r="R22" s="68"/>
+    </row>
+    <row r="23" spans="1:18" ht="15" customHeight="1">
+      <c r="A23" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F23" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G23" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K23" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L23" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O23" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="P23" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q23" s="68"/>
+      <c r="R23" s="68"/>
+    </row>
+    <row r="24" spans="1:18" ht="15" customHeight="1">
+      <c r="A24" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F24" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G24" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="I24" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L24" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M24" s="68"/>
+      <c r="N24" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O24" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P24" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q24" s="68"/>
+      <c r="R24" s="68"/>
+    </row>
+    <row r="25" spans="1:18" ht="15" customHeight="1">
+      <c r="A25" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F25" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G25" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="I25" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L25" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M25" s="68"/>
+      <c r="N25" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O25" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P25" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q25" s="68"/>
+      <c r="R25" s="68"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" customHeight="1">
+      <c r="A26" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F26" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G26" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="68" t="s">
+        <v>279</v>
+      </c>
+      <c r="I26" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L26" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O26" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P26" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q26" s="68"/>
+      <c r="R26" s="68"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" customHeight="1">
+      <c r="A27" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F27" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G27" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="68" t="s">
+        <v>280</v>
+      </c>
+      <c r="I27" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K27" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L27" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M27" s="68"/>
+      <c r="N27" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O27" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P27" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q27" s="68"/>
+      <c r="R27" s="68"/>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F28" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G28" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="68" t="s">
+        <v>281</v>
+      </c>
+      <c r="I28" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K28" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L28" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O28" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P28" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" s="68"/>
+      <c r="R28" s="68"/>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F29" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G29" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="I29" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K29" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L29" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O29" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P29" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F30" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G30" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="I30" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K30" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L30" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M30" s="68"/>
+      <c r="N30" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O30" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P30" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q30" s="68"/>
+      <c r="R30" s="68"/>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F31" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G31" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="I31" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K31" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L31" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M31" s="68"/>
+      <c r="N31" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O31" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P31" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q31" s="68"/>
+      <c r="R31" s="68"/>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F32" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G32" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="I32" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K32" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L32" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M32" s="68"/>
+      <c r="N32" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P32" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q32" s="68"/>
+      <c r="R32" s="68"/>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F33" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G33" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="I33" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L33" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M33" s="68"/>
+      <c r="N33" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O33" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P33" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q33" s="68"/>
+      <c r="R33" s="68"/>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F34" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G34" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="I34" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K34" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L34" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M34" s="68"/>
+      <c r="N34" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O34" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P34" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q34" s="68"/>
+      <c r="R34" s="68"/>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F35" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G35" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L35" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M35" s="68"/>
+      <c r="N35" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O35" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P35" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q35" s="68"/>
+      <c r="R35" s="68"/>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F36" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G36" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="I36" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K36" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L36" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M36" s="68"/>
+      <c r="N36" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="O36" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P36" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q36" s="68"/>
+      <c r="R36" s="68"/>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F37" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G37" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="I37" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K37" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L37" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M37" s="68"/>
+      <c r="N37" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O37" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q37" s="68"/>
+      <c r="R37" s="68"/>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F38" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G38" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="I38" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K38" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L38" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M38" s="68"/>
+      <c r="N38" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O38" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q38" s="68"/>
+      <c r="R38" s="68"/>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F39" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G39" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="I39" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K39" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L39" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M39" s="68"/>
+      <c r="N39" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O39" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P39" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q39" s="68"/>
+      <c r="R39" s="68"/>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F40" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G40" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K40" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L40" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M40" s="68"/>
+      <c r="N40" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O40" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P40" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q40" s="68"/>
+      <c r="R40" s="68"/>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F41" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G41" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="68" t="s">
+        <v>195</v>
+      </c>
+      <c r="I41" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K41" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L41" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M41" s="68"/>
+      <c r="N41" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O41" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P41" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q41" s="68"/>
+      <c r="R41" s="68"/>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F42" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G42" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="68" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K42" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L42" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M42" s="68"/>
+      <c r="N42" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O42" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P42" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q42" s="68"/>
+      <c r="R42" s="68"/>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F43" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G43" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="I43" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K43" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L43" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M43" s="68"/>
+      <c r="N43" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O43" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P43" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q43" s="68"/>
+      <c r="R43" s="68"/>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F44" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G44" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="68" t="s">
+        <v>198</v>
+      </c>
+      <c r="I44" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K44" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L44" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M44" s="68"/>
+      <c r="N44" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O44" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P44" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q44" s="68"/>
+      <c r="R44" s="68"/>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F45" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G45" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="I45" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K45" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L45" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M45" s="68"/>
+      <c r="N45" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O45" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P45" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="68"/>
+      <c r="R45" s="68"/>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F46" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G46" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="68" t="s">
+        <v>200</v>
+      </c>
+      <c r="I46" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K46" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L46" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M46" s="68"/>
+      <c r="N46" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O46" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P46" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="68"/>
+      <c r="R46" s="68"/>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F47" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G47" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="I47" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K47" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L47" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M47" s="68"/>
+      <c r="N47" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O47" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P47" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="68"/>
+      <c r="R47" s="68"/>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F48" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G48" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="I48" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K48" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L48" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M48" s="68"/>
+      <c r="N48" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O48" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P48" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="68"/>
+      <c r="R48" s="68"/>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F49" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G49" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="68" t="s">
+        <v>283</v>
+      </c>
+      <c r="I49" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K49" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L49" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M49" s="68"/>
+      <c r="N49" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="O49" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P49" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q49" s="68"/>
+      <c r="R49" s="68"/>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F50" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G50" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="I50" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K50" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L50" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M50" s="68"/>
+      <c r="N50" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="O50" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P50" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q50" s="68"/>
+      <c r="R50" s="68"/>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G51" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="I51" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K51" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L51" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M51" s="68"/>
+      <c r="N51" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="O51" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P51" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q51" s="68"/>
+      <c r="R51" s="68"/>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F52" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G52" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="I52" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K52" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L52" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M52" s="68"/>
+      <c r="N52" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="O52" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P52" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q52" s="68"/>
+      <c r="R52" s="68"/>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F53" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G53" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="I53" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K53" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L53" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M53" s="68"/>
+      <c r="N53" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="O53" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P53" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q53" s="68"/>
+      <c r="R53" s="68"/>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="68"/>
+      <c r="E54" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F54" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G54" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="68" t="s">
+        <v>206</v>
+      </c>
+      <c r="I54" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K54" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L54" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M54" s="68"/>
+      <c r="N54" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="O54" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="P54" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q54" s="68"/>
+      <c r="R54" s="68"/>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="68"/>
+      <c r="E55" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F55" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G55" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="I55" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="K55" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L55" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M55" s="68"/>
+      <c r="N55" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O55" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P55" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q55" s="68"/>
+      <c r="R55" s="68"/>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="68"/>
+      <c r="E56" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F56" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G56" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="I56" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="K56" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L56" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M56" s="68"/>
+      <c r="N56" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O56" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P56" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q56" s="68"/>
+      <c r="R56" s="68"/>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="68"/>
+      <c r="E57" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F57" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G57" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="68" t="s">
+        <v>209</v>
+      </c>
+      <c r="I57" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="K57" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L57" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M57" s="68"/>
+      <c r="N57" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O57" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P57" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q57" s="68"/>
+      <c r="R57" s="68"/>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B58" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" s="68"/>
+      <c r="E58" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F58" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G58" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="I58" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="K58" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L58" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M58" s="68"/>
+      <c r="N58" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O58" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P58" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q58" s="68"/>
+      <c r="R58" s="68"/>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B59" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C59" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="68"/>
+      <c r="E59" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F59" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G59" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I59" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="K59" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L59" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M59" s="68"/>
+      <c r="N59" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O59" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P59" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q59" s="68"/>
+      <c r="R59" s="68"/>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B60" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" s="68"/>
+      <c r="E60" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F60" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G60" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="68" t="s">
+        <v>212</v>
+      </c>
+      <c r="I60" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K60" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L60" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M60" s="68"/>
+      <c r="N60" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O60" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P60" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q60" s="68"/>
+      <c r="R60" s="68"/>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="68"/>
+      <c r="E61" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F61" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G61" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="I61" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K61" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L61" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M61" s="68"/>
+      <c r="N61" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O61" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P61" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q61" s="68"/>
+      <c r="R61" s="68"/>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62" s="68"/>
+      <c r="E62" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F62" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G62" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="I62" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J62" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K62" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L62" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M62" s="68"/>
+      <c r="N62" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O62" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P62" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q62" s="68"/>
+      <c r="R62" s="68"/>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63" s="68"/>
+      <c r="E63" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F63" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G63" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" s="68" t="s">
+        <v>287</v>
+      </c>
+      <c r="I63" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K63" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L63" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M63" s="68"/>
+      <c r="N63" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O63" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P63" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="C64" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F64" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G64" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="I64" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K64" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L64" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M64" s="68"/>
+      <c r="N64" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O64" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P64" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q64" s="68"/>
+      <c r="R64" s="68"/>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="C65" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F65" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G65" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="I65" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K65" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L65" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M65" s="68"/>
+      <c r="N65" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O65" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P65" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q65" s="68"/>
+      <c r="R65" s="68"/>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F66" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G66" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="68" t="s">
+        <v>288</v>
+      </c>
+      <c r="I66" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K66" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L66" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M66" s="68"/>
+      <c r="N66" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O66" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P66" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C67" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F67" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G67" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="I67" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J67" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K67" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L67" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M67" s="68"/>
+      <c r="N67" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O67" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P67" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q67" s="68"/>
+      <c r="R67" s="68"/>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C68" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F68" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G68" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="68" t="s">
+        <v>217</v>
+      </c>
+      <c r="I68" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J68" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K68" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L68" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M68" s="68"/>
+      <c r="N68" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O68" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P68" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q68" s="68"/>
+      <c r="R68" s="68"/>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="A69" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B69" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C69" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F69" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G69" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="I69" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L69" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M69" s="68"/>
+      <c r="N69" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O69" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P69" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q69" s="68"/>
+      <c r="R69" s="68"/>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="A70" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C70" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D70" s="68"/>
+      <c r="E70" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F70" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G70" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="68" t="s">
+        <v>219</v>
+      </c>
+      <c r="I70" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L70" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M70" s="68"/>
+      <c r="N70" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O70" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P70" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q70" s="68"/>
+      <c r="R70" s="68"/>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="A71" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="C71" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D71" s="68"/>
+      <c r="E71" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F71" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G71" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="I71" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J71" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K71" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L71" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M71" s="68"/>
+      <c r="N71" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O71" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P71" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q71" s="68"/>
+      <c r="R71" s="68"/>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="A72" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="68"/>
+      <c r="E72" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F72" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G72" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="I72" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K72" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L72" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M72" s="68"/>
+      <c r="N72" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O72" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P72" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q72" s="68"/>
+      <c r="R72" s="68"/>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="A73" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D73" s="68"/>
+      <c r="E73" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F73" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G73" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="I73" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J73" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K73" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L73" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M73" s="68"/>
+      <c r="N73" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O73" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P73" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q73" s="68"/>
+      <c r="R73" s="68"/>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="D74" s="68"/>
+      <c r="E74" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F74" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G74" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="I74" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J74" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K74" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L74" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M74" s="68"/>
+      <c r="N74" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O74" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P74" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q74" s="68"/>
+      <c r="R74" s="68"/>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="D75" s="68"/>
+      <c r="E75" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F75" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G75" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H75" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="I75" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J75" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K75" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L75" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M75" s="68"/>
+      <c r="N75" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O75" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P75" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q75" s="68"/>
+      <c r="R75" s="68"/>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="D76" s="68"/>
+      <c r="E76" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F76" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G76" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" s="68" t="s">
+        <v>291</v>
+      </c>
+      <c r="I76" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K76" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L76" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M76" s="68"/>
+      <c r="N76" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O76" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P76" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q76" s="68"/>
+      <c r="R76" s="68"/>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C77" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="D77" s="68"/>
+      <c r="E77" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F77" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G77" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="I77" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J77" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="K77" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L77" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M77" s="68"/>
+      <c r="N77" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O77" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P77" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q77" s="68"/>
+      <c r="R77" s="68"/>
+    </row>
+    <row r="78" spans="1:18">
+      <c r="A78" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B78" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C78" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D78" s="68"/>
+      <c r="E78" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F78" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G78" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="I78" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K78" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L78" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M78" s="68"/>
+      <c r="N78" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="O78" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P78" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q78" s="68"/>
+      <c r="R78" s="68"/>
+    </row>
+    <row r="79" spans="1:18">
+      <c r="A79" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B79" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="68"/>
+      <c r="E79" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F79" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G79" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="68" t="s">
+        <v>226</v>
+      </c>
+      <c r="I79" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J79" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K79" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L79" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M79" s="68"/>
+      <c r="N79" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="O79" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P79" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q79" s="68"/>
+      <c r="R79" s="68"/>
+    </row>
+    <row r="80" spans="1:18">
+      <c r="A80" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B80" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C80" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F80" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G80" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="I80" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K80" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L80" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M80" s="68"/>
+      <c r="N80" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="O80" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P80" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q80" s="68"/>
+      <c r="R80" s="68"/>
+    </row>
+    <row r="81" spans="1:18">
+      <c r="A81" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C81" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F81" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G81" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="I81" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J81" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K81" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L81" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M81" s="68"/>
+      <c r="N81" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="O81" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P81" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q81" s="68"/>
+      <c r="R81" s="68"/>
+    </row>
+    <row r="82" spans="1:18">
+      <c r="A82" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B82" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D82" s="68"/>
+      <c r="E82" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F82" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G82" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="I82" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J82" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K82" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L82" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M82" s="68"/>
+      <c r="N82" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O82" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="P82" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q82" s="68"/>
+      <c r="R82" s="68"/>
+    </row>
+    <row r="83" spans="1:18">
+      <c r="A83" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B83" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C83" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F83" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G83" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="68" t="s">
+        <v>229</v>
+      </c>
+      <c r="I83" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J83" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K83" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L83" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M83" s="68"/>
+      <c r="N83" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O83" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="P83" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q83" s="68"/>
+      <c r="R83" s="68"/>
+    </row>
+    <row r="84" spans="1:18">
+      <c r="A84" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B84" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C84" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F84" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G84" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="I84" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J84" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K84" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L84" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M84" s="68"/>
+      <c r="N84" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O84" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="P84" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q84" s="68"/>
+      <c r="R84" s="68"/>
+    </row>
+    <row r="85" spans="1:18">
+      <c r="A85" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B85" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C85" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F85" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G85" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="68" t="s">
+        <v>294</v>
+      </c>
+      <c r="I85" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J85" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K85" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L85" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M85" s="68"/>
+      <c r="N85" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O85" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="P85" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q85" s="68"/>
+      <c r="R85" s="68"/>
+    </row>
+    <row r="86" spans="1:18">
+      <c r="A86" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B86" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C86" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D86" s="68"/>
+      <c r="E86" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F86" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G86" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="I86" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J86" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K86" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L86" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M86" s="68"/>
+      <c r="N86" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="O86" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="P86" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q86" s="68"/>
+      <c r="R86" s="68"/>
+    </row>
+    <row r="87" spans="1:18">
+      <c r="A87" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B87" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C87" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F87" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G87" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="I87" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J87" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K87" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L87" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M87" s="68"/>
+      <c r="N87" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O87" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P87" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q87" s="68"/>
+      <c r="R87" s="68"/>
+    </row>
+    <row r="88" spans="1:18">
+      <c r="A88" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B88" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F88" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G88" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="68" t="s">
+        <v>230</v>
+      </c>
+      <c r="I88" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J88" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K88" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L88" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M88" s="68"/>
+      <c r="N88" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O88" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P88" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q88" s="68"/>
+      <c r="R88" s="68"/>
+    </row>
+    <row r="89" spans="1:18">
+      <c r="A89" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B89" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C89" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="D89" s="68"/>
+      <c r="E89" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F89" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G89" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="68" t="s">
+        <v>232</v>
+      </c>
+      <c r="I89" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J89" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K89" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L89" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M89" s="68"/>
+      <c r="N89" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O89" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P89" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q89" s="68"/>
+      <c r="R89" s="68"/>
+    </row>
+    <row r="90" spans="1:18">
+      <c r="A90" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C90" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F90" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G90" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="I90" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J90" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K90" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L90" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M90" s="68"/>
+      <c r="N90" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O90" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P90" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q90" s="68"/>
+      <c r="R90" s="68"/>
+    </row>
+    <row r="91" spans="1:18">
+      <c r="A91" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B91" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F91" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G91" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="I91" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J91" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K91" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L91" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M91" s="68"/>
+      <c r="N91" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O91" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P91" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q91" s="68"/>
+      <c r="R91" s="68"/>
+    </row>
+    <row r="92" spans="1:18">
+      <c r="A92" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B92" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D92" s="68"/>
+      <c r="E92" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F92" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G92" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="I92" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J92" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K92" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L92" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M92" s="68"/>
+      <c r="N92" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O92" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P92" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q92" s="68"/>
+      <c r="R92" s="68"/>
+    </row>
+    <row r="93" spans="1:18">
+      <c r="A93" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B93" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F93" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G93" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" s="68" t="s">
+        <v>235</v>
+      </c>
+      <c r="I93" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J93" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K93" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L93" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M93" s="68"/>
+      <c r="N93" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O93" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P93" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q93" s="68"/>
+      <c r="R93" s="68"/>
+    </row>
+    <row r="94" spans="1:18">
+      <c r="A94" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B94" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C94" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F94" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G94" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="I94" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J94" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K94" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L94" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M94" s="68"/>
+      <c r="N94" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O94" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P94" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q94" s="68"/>
+      <c r="R94" s="68"/>
+    </row>
+    <row r="95" spans="1:18">
+      <c r="A95" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B95" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C95" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F95" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G95" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" s="68" t="s">
+        <v>237</v>
+      </c>
+      <c r="I95" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J95" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K95" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L95" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M95" s="68"/>
+      <c r="N95" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O95" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P95" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q95" s="68"/>
+      <c r="R95" s="68"/>
+    </row>
+    <row r="96" spans="1:18">
+      <c r="A96" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B96" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F96" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G96" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" s="68" t="s">
+        <v>238</v>
+      </c>
+      <c r="I96" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J96" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K96" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L96" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M96" s="68"/>
+      <c r="N96" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O96" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P96" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q96" s="68"/>
+      <c r="R96" s="68"/>
+    </row>
+    <row r="97" spans="1:18">
+      <c r="A97" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B97" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D97" s="68"/>
+      <c r="E97" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F97" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G97" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="I97" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J97" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K97" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L97" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M97" s="68"/>
+      <c r="N97" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O97" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P97" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q97" s="68"/>
+      <c r="R97" s="68"/>
+    </row>
+    <row r="98" spans="1:18">
+      <c r="A98" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B98" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F98" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G98" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="I98" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J98" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K98" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L98" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M98" s="68"/>
+      <c r="N98" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O98" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P98" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q98" s="68"/>
+      <c r="R98" s="68"/>
+    </row>
+    <row r="99" spans="1:18">
+      <c r="A99" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B99" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C99" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F99" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G99" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="68" t="s">
+        <v>241</v>
+      </c>
+      <c r="I99" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J99" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K99" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L99" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M99" s="68"/>
+      <c r="N99" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O99" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P99" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q99" s="68"/>
+      <c r="R99" s="68"/>
+    </row>
+    <row r="100" spans="1:18">
+      <c r="A100" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B100" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C100" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F100" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G100" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H100" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="I100" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J100" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K100" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L100" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M100" s="68"/>
+      <c r="N100" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O100" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P100" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q100" s="68"/>
+      <c r="R100" s="68"/>
+    </row>
+    <row r="101" spans="1:18">
+      <c r="A101" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B101" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D101" s="68"/>
+      <c r="E101" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F101" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G101" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" s="68" t="s">
+        <v>243</v>
+      </c>
+      <c r="I101" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J101" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K101" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L101" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M101" s="68"/>
+      <c r="N101" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O101" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P101" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q101" s="68"/>
+      <c r="R101" s="68"/>
+    </row>
+    <row r="102" spans="1:18">
+      <c r="A102" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B102" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C102" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D102" s="68"/>
+      <c r="E102" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F102" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G102" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102" s="68" t="s">
+        <v>244</v>
+      </c>
+      <c r="I102" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J102" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K102" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L102" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M102" s="68"/>
+      <c r="N102" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O102" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P102" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q102" s="68"/>
+      <c r="R102" s="68"/>
+    </row>
+    <row r="103" spans="1:18">
+      <c r="A103" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B103" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C103" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D103" s="68"/>
+      <c r="E103" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F103" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G103" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" s="68" t="s">
+        <v>245</v>
+      </c>
+      <c r="I103" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J103" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K103" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L103" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M103" s="68"/>
+      <c r="N103" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O103" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P103" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q103" s="68"/>
+      <c r="R103" s="68"/>
+    </row>
+    <row r="104" spans="1:18">
+      <c r="A104" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B104" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C104" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F104" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G104" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="I104" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J104" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K104" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L104" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M104" s="68"/>
+      <c r="N104" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O104" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P104" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q104" s="68"/>
+      <c r="R104" s="68"/>
+    </row>
+    <row r="105" spans="1:18">
+      <c r="A105" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C105" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F105" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G105" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="68" t="s">
+        <v>247</v>
+      </c>
+      <c r="I105" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J105" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K105" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L105" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M105" s="68"/>
+      <c r="N105" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O105" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P105" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q105" s="68"/>
+      <c r="R105" s="68"/>
+    </row>
+    <row r="106" spans="1:18">
+      <c r="A106" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B106" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C106" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D106" s="68"/>
+      <c r="E106" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F106" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G106" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H106" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="I106" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J106" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K106" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L106" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M106" s="68"/>
+      <c r="N106" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O106" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P106" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q106" s="68"/>
+      <c r="R106" s="68"/>
+    </row>
+    <row r="107" spans="1:18">
+      <c r="A107" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B107" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C107" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F107" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G107" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="68" t="s">
+        <v>249</v>
+      </c>
+      <c r="I107" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J107" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K107" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L107" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M107" s="68"/>
+      <c r="N107" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O107" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P107" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q107" s="68"/>
+      <c r="R107" s="68"/>
+    </row>
+    <row r="108" spans="1:18">
+      <c r="A108" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B108" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C108" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F108" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G108" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="I108" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J108" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K108" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L108" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M108" s="68"/>
+      <c r="N108" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O108" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P108" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q108" s="68"/>
+      <c r="R108" s="68"/>
+    </row>
+    <row r="109" spans="1:18">
+      <c r="A109" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="C109" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="D109" s="68"/>
+      <c r="E109" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F109" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G109" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" s="68" t="s">
+        <v>251</v>
+      </c>
+      <c r="I109" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J109" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K109" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L109" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M109" s="68"/>
+      <c r="N109" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O109" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P109" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q109" s="68"/>
+      <c r="R109" s="68"/>
+    </row>
+    <row r="110" spans="1:18">
+      <c r="A110" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B110" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="C110" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="D110" s="68"/>
+      <c r="E110" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F110" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G110" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="I110" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J110" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K110" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L110" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M110" s="68"/>
+      <c r="N110" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O110" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P110" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q110" s="68"/>
+      <c r="R110" s="68"/>
+    </row>
+    <row r="111" spans="1:18">
+      <c r="A111" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B111" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="C111" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="D111" s="68"/>
+      <c r="E111" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F111" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G111" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="I111" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J111" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K111" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L111" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M111" s="68"/>
+      <c r="N111" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O111" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P111" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q111" s="68"/>
+      <c r="R111" s="68"/>
+    </row>
+    <row r="112" spans="1:18">
+      <c r="A112" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B112" s="68" t="s">
+        <v>145</v>
+      </c>
+      <c r="C112" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="D112" s="68"/>
+      <c r="E112" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F112" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G112" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="I112" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J112" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K112" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L112" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M112" s="68"/>
+      <c r="N112" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O112" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="P112" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q112" s="68"/>
+      <c r="R112" s="68"/>
+    </row>
+    <row r="113" spans="1:18">
+      <c r="A113" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B113" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C113" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D113" s="68"/>
+      <c r="E113" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F113" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G113" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H113" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="I113" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J113" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K113" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L113" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M113" s="68"/>
+      <c r="N113" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="O113" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P113" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q113" s="68"/>
+      <c r="R113" s="68"/>
+    </row>
+    <row r="114" spans="1:18">
+      <c r="A114" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B114" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C114" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D114" s="68"/>
+      <c r="E114" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F114" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G114" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H114" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="I114" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J114" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K114" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L114" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M114" s="68"/>
+      <c r="N114" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="O114" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P114" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q114" s="68"/>
+      <c r="R114" s="68"/>
+    </row>
+    <row r="115" spans="1:18">
+      <c r="A115" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B115" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C115" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D115" s="68"/>
+      <c r="E115" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F115" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G115" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H115" s="68" t="s">
+        <v>257</v>
+      </c>
+      <c r="I115" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J115" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K115" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L115" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M115" s="68"/>
+      <c r="N115" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="O115" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P115" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q115" s="68"/>
+      <c r="R115" s="68"/>
+    </row>
+    <row r="116" spans="1:18">
+      <c r="A116" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B116" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C116" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D116" s="68"/>
+      <c r="E116" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F116" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G116" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="I116" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J116" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="K116" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L116" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M116" s="68"/>
+      <c r="N116" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="O116" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P116" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q116" s="68"/>
+      <c r="R116" s="68"/>
+    </row>
+    <row r="117" spans="1:18">
+      <c r="A117" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B117" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C117" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D117" s="68"/>
+      <c r="E117" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F117" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G117" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H117" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="I117" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J117" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K117" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L117" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M117" s="68"/>
+      <c r="N117" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O117" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P117" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q117" s="68"/>
+      <c r="R117" s="68"/>
+    </row>
+    <row r="118" spans="1:18">
+      <c r="A118" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B118" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C118" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D118" s="68"/>
+      <c r="E118" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F118" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G118" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H118" s="68" t="s">
+        <v>260</v>
+      </c>
+      <c r="I118" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J118" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K118" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L118" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M118" s="68"/>
+      <c r="N118" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O118" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P118" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q118" s="68"/>
+      <c r="R118" s="68"/>
+    </row>
+    <row r="119" spans="1:18">
+      <c r="A119" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B119" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D119" s="68"/>
+      <c r="E119" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F119" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G119" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H119" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="I119" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J119" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K119" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L119" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M119" s="68"/>
+      <c r="N119" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O119" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P119" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q119" s="68"/>
+      <c r="R119" s="68"/>
+    </row>
+    <row r="120" spans="1:18">
+      <c r="A120" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B120" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C120" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D120" s="68"/>
+      <c r="E120" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F120" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G120" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H120" s="68" t="s">
+        <v>299</v>
+      </c>
+      <c r="I120" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J120" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K120" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L120" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M120" s="68"/>
+      <c r="N120" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O120" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P120" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q120" s="68"/>
+      <c r="R120" s="68"/>
+    </row>
+    <row r="121" spans="1:18">
+      <c r="A121" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B121" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C121" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D121" s="68"/>
+      <c r="E121" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F121" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G121" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H121" s="68" t="s">
+        <v>300</v>
+      </c>
+      <c r="I121" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J121" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K121" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L121" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M121" s="68"/>
+      <c r="N121" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O121" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P121" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q121" s="68"/>
+      <c r="R121" s="68"/>
+    </row>
+    <row r="122" spans="1:18">
+      <c r="A122" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B122" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C122" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D122" s="68"/>
+      <c r="E122" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F122" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G122" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H122" s="68" t="s">
+        <v>262</v>
+      </c>
+      <c r="I122" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J122" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K122" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L122" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M122" s="68"/>
+      <c r="N122" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O122" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P122" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q122" s="68"/>
+      <c r="R122" s="68"/>
+    </row>
+    <row r="123" spans="1:18">
+      <c r="A123" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B123" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C123" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="D123" s="68"/>
+      <c r="E123" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F123" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G123" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H123" s="68" t="s">
+        <v>263</v>
+      </c>
+      <c r="I123" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J123" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K123" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L123" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M123" s="68"/>
+      <c r="N123" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O123" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P123" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q123" s="68"/>
+      <c r="R123" s="68"/>
+    </row>
+    <row r="124" spans="1:18">
+      <c r="A124" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B124" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="D124" s="68"/>
+      <c r="E124" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F124" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G124" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H124" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="I124" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J124" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K124" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L124" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M124" s="68"/>
+      <c r="N124" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O124" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P124" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q124" s="68"/>
+      <c r="R124" s="68"/>
+    </row>
+    <row r="125" spans="1:18">
+      <c r="A125" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B125" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C125" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="D125" s="68"/>
+      <c r="E125" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F125" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G125" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H125" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="I125" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J125" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K125" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L125" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M125" s="68"/>
+      <c r="N125" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O125" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P125" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q125" s="68"/>
+      <c r="R125" s="68"/>
+    </row>
+    <row r="126" spans="1:18">
+      <c r="A126" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B126" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C126" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="D126" s="68"/>
+      <c r="E126" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F126" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G126" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="I126" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J126" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K126" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L126" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M126" s="68"/>
+      <c r="N126" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O126" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P126" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q126" s="68"/>
+      <c r="R126" s="68"/>
+    </row>
+    <row r="127" spans="1:18">
+      <c r="A127" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B127" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="C127" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="D127" s="68"/>
+      <c r="E127" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="F127" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G127" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H127" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="I127" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J127" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K127" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="L127" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="M127" s="68"/>
+      <c r="N127" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="O127" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="P127" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q127" s="68"/>
+      <c r="R127" s="68"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>